--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123619785</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123620064</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123619785</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123620064</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123619785</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123620064</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123620064</v>
+        <v>124056822</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>90940</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalekullen, Dalekullen, Boh</t>
+          <t>Hällekas, Hällekas, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317169</v>
+        <v>317046</v>
       </c>
       <c r="R3" t="n">
-        <v>6474267</v>
+        <v>6474190</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +886,454 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124057136</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56799</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hällekas, Hällekas, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>317046</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6474190</v>
+      </c>
+      <c r="S4" t="n">
+        <v>30</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Herrestad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Zim Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Zim Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124057011</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57861</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hällekas, Hällekas, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>317046</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6474190</v>
+      </c>
+      <c r="S5" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Herrestad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Zim Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Zim Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124056596</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78987</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1642</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Långskägg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Usnea longissima</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dalekullen, Dalekullen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>317095</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6474299</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Herrestad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Zim Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Zim Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123620064</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dalekullen, Dalekullen, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>317169</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6474267</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Herrestad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Zim Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Zim Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124057011</v>
+        <v>124056596</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>78987</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,46 +1018,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1642</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällekas, Hällekas, Boh</t>
+          <t>Dalekullen, Dalekullen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317046</v>
+        <v>317095</v>
       </c>
       <c r="R5" t="n">
-        <v>6474190</v>
+        <v>6474299</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:40</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124056596</v>
+        <v>124057011</v>
       </c>
       <c r="B6" t="n">
-        <v>78987</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1120,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1642</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalekullen, Dalekullen, Boh</t>
+          <t>Hällekas, Hällekas, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317095</v>
+        <v>317046</v>
       </c>
       <c r="R6" t="n">
-        <v>6474299</v>
+        <v>6474190</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124057136</v>
+        <v>124056596</v>
       </c>
       <c r="B4" t="n">
-        <v>56799</v>
+        <v>78987</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,46 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>1642</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällekas, Hällekas, Boh</t>
+          <t>Dalekullen, Dalekullen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317046</v>
+        <v>317095</v>
       </c>
       <c r="R4" t="n">
-        <v>6474190</v>
+        <v>6474299</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,22 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124056596</v>
+        <v>124057011</v>
       </c>
       <c r="B5" t="n">
-        <v>78987</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,41 +1003,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1642</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalekullen, Dalekullen, Boh</t>
+          <t>Hällekas, Hällekas, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317095</v>
+        <v>317046</v>
       </c>
       <c r="R5" t="n">
-        <v>6474299</v>
+        <v>6474190</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,12 +1066,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124057011</v>
+        <v>124057136</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>56799</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,22 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124056822</v>
+        <v>124057011</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,28 +799,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -833,7 +838,7 @@
         <v>6474190</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,9 +865,19 @@
           <t>2025-04-13</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -991,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124057011</v>
+        <v>124056822</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>90940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,33 +1018,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -1042,7 +1052,7 @@
         <v>6474190</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,19 +1079,9 @@
           <t>2025-04-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124057136</v>
+        <v>124056596</v>
       </c>
       <c r="B3" t="n">
-        <v>56821</v>
+        <v>79009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>1642</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällekas, Hällekas, Boh</t>
+          <t>Dalekullen, Dalekullen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317046</v>
+        <v>317095</v>
       </c>
       <c r="R3" t="n">
-        <v>6474190</v>
+        <v>6474299</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124056822</v>
+        <v>124057011</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,28 +901,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -950,7 +940,7 @@
         <v>6474190</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,9 +967,19 @@
           <t>2025-04-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124057011</v>
+        <v>124057136</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>56821</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124056596</v>
+        <v>124056822</v>
       </c>
       <c r="B6" t="n">
-        <v>79009</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1642</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalekullen, Dalekullen, Boh</t>
+          <t>Hällekas, Hällekas, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317095</v>
+        <v>317046</v>
       </c>
       <c r="R6" t="n">
-        <v>6474299</v>
+        <v>6474190</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124057136</v>
+        <v>124056822</v>
       </c>
       <c r="B5" t="n">
-        <v>56821</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,33 +1018,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -1057,7 +1052,7 @@
         <v>6474190</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124056822</v>
+        <v>124057136</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>56821</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,28 +1120,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -1169,7 +1159,7 @@
         <v>6474190</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124057011</v>
+        <v>124056822</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,33 +901,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -940,7 +935,7 @@
         <v>6474190</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,19 +962,9 @@
           <t>2025-04-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124056822</v>
+        <v>124057011</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,28 +1003,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -1052,7 +1042,7 @@
         <v>6474190</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,9 +1069,19 @@
           <t>2025-04-13</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124056822</v>
+        <v>124057011</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,28 +901,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -935,7 +940,7 @@
         <v>6474190</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,9 +967,19 @@
           <t>2025-04-13</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124057011</v>
+        <v>124056822</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,33 +1018,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -1042,7 +1052,7 @@
         <v>6474190</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,19 +1079,9 @@
           <t>2025-04-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124056596</v>
+        <v>124057136</v>
       </c>
       <c r="B3" t="n">
-        <v>79009</v>
+        <v>56821</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1642</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalekullen, Dalekullen, Boh</t>
+          <t>Hällekas, Hällekas, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317095</v>
+        <v>317046</v>
       </c>
       <c r="R3" t="n">
-        <v>6474299</v>
+        <v>6474190</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124057011</v>
+        <v>124056822</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,33 +916,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -940,7 +950,7 @@
         <v>6474190</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,19 +977,9 @@
           <t>2025-04-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124056822</v>
+        <v>124057011</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,28 +1018,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -1052,7 +1057,7 @@
         <v>6474190</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,9 +1084,19 @@
           <t>2025-04-13</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124057136</v>
+        <v>124056596</v>
       </c>
       <c r="B6" t="n">
-        <v>56821</v>
+        <v>79009</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,46 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100038</v>
+        <v>1642</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hällekas, Hällekas, Boh</t>
+          <t>Dalekullen, Dalekullen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317046</v>
+        <v>317095</v>
       </c>
       <c r="R6" t="n">
-        <v>6474190</v>
+        <v>6474299</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,22 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124057136</v>
+        <v>124056822</v>
       </c>
       <c r="B3" t="n">
-        <v>56821</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,33 +799,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100038</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -838,7 +833,7 @@
         <v>6474190</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>19:40</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124056822</v>
+        <v>124057136</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>56821</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,28 +901,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hällekas, Hällekas, Boh</t>
@@ -950,7 +940,7 @@
         <v>6474190</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +964,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123619785</v>
+        <v>124056822</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalekullen, Dalekullen, Boh</t>
+          <t>Hällekas, Hällekas, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317128</v>
+        <v>317046</v>
       </c>
       <c r="R2" t="n">
-        <v>6474274</v>
+        <v>6474190</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:36</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124056822</v>
+        <v>124056596</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>1642</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällekas, Hällekas, Boh</t>
+          <t>Dalekullen, Dalekullen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317046</v>
+        <v>317095</v>
       </c>
       <c r="R3" t="n">
-        <v>6474190</v>
+        <v>6474299</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,58 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124057136</v>
+        <v>123619785</v>
       </c>
       <c r="B4" t="n">
-        <v>56821</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällekas, Hällekas, Boh</t>
+          <t>Dalekullen, Dalekullen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317046</v>
+        <v>317128</v>
       </c>
       <c r="R4" t="n">
-        <v>6474190</v>
+        <v>6474274</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,22 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,58 +976,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124057011</v>
+        <v>123620064</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hällekas, Hällekas, Boh</t>
+          <t>Dalekullen, Dalekullen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317046</v>
+        <v>317169</v>
       </c>
       <c r="R5" t="n">
-        <v>6474190</v>
+        <v>6474267</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1041,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,53 +1083,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124056596</v>
+        <v>124057136</v>
       </c>
       <c r="B6" t="n">
-        <v>79009</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1642</v>
+        <v>100038</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalekullen, Dalekullen, Boh</t>
+          <t>Hällekas, Hällekas, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317095</v>
+        <v>317046</v>
       </c>
       <c r="R6" t="n">
-        <v>6474299</v>
+        <v>6474190</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1153,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,53 +1195,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123620064</v>
+        <v>124057011</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dalekullen, Dalekullen, Boh</t>
+          <t>Hällekas, Hällekas, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317169</v>
+        <v>317046</v>
       </c>
       <c r="R7" t="n">
-        <v>6474267</v>
+        <v>6474190</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,22 +1265,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1304,118 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118894684</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Korset, Kurveröd, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>316991</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6474337</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Herrestad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11824-2025 artfynd.xlsx
+++ b/artfynd/A 11824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124056822</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124056596</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123619785</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123620064</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124057136</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124057011</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,8 +1451,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118894684</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>